--- a/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Quillón</t>
   </si>
   <si>
+    <t xml:space="preserve">Coelemu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
-    <t xml:space="preserve">Coelemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
@@ -81,12 +81,12 @@
     <t xml:space="preserve">San Carlos</t>
   </si>
   <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bulnes</t>
   </si>
   <si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -541,7 +541,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>191.91</v>
+        <v>207.66</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>168.32</v>
+        <v>181.28</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>160.84</v>
+        <v>173.99</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>157.91</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>155.05</v>
+        <v>166.71</v>
       </c>
     </row>
     <row r="7">
@@ -626,7 +626,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>151.71</v>
+        <v>164.16</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>138.14</v>
+        <v>147.62</v>
       </c>
     </row>
     <row r="9">
@@ -654,13 +654,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>16106</v>
+        <v>16203</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>128.28</v>
+        <v>136.55</v>
       </c>
     </row>
     <row r="10">
@@ -671,13 +671,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>16203</v>
+        <v>16106</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>127.18</v>
+        <v>136.52</v>
       </c>
     </row>
     <row r="11">
@@ -694,7 +694,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>127.18</v>
+        <v>136.19</v>
       </c>
     </row>
     <row r="12">
@@ -711,7 +711,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>125.78</v>
+        <v>135.73</v>
       </c>
     </row>
     <row r="13">
@@ -728,7 +728,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>122.95</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="14">
@@ -745,7 +745,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>118.81</v>
+        <v>127.26</v>
       </c>
     </row>
     <row r="15">
@@ -762,7 +762,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>115.05</v>
+        <v>124.58</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>114.07</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="17">
@@ -790,13 +790,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>16109</v>
+        <v>16105</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>112.52</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="18">
@@ -807,13 +807,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>16105</v>
+        <v>16109</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>111.81</v>
+        <v>120.58</v>
       </c>
     </row>
     <row r="19">
@@ -830,7 +830,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>111.74</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="20">
@@ -847,7 +847,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>99.59</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="21">
@@ -864,7 +864,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>87.52</v>
+        <v>93.76</v>
       </c>
     </row>
     <row r="22">
@@ -881,7 +881,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>76.95</v>
+        <v>82.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Portezuelo</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:16</t>
+    <t xml:space="preserve">2026-10-04 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:41</t>
+    <t xml:space="preserve">2026-10-05 16:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
